--- a/src/attributions/attributions_ig_traj_466.xlsx
+++ b/src/attributions/attributions_ig_traj_466.xlsx
@@ -1568,19 +1568,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.04108131662478072</v>
+        <v>0.03643237185000936</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08702041426650835</v>
+        <v>0.02858021506782762</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.04064150291246865</v>
+        <v>-0.02112287465416252</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -1592,22 +1592,22 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.07363174393209765</v>
+        <v>0.09481264635247114</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0040084651453178</v>
+        <v>0.001052549632037288</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007924801489527527</v>
+        <v>0.003482910366585674</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1619,22 +1619,22 @@
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1101144472506266</v>
+        <v>-0.02262198082371396</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02917347449071652</v>
+        <v>0.02670688603981957</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01343745237300837</v>
+        <v>-0.04396502301331968</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
@@ -1646,55 +1646,55 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01330187165430504</v>
+        <v>0.009356524373093514</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.01074822284980047</v>
+        <v>-0.01876015811119724</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.06233918606274665</v>
+        <v>-0.01015412408536794</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02184165663472595</v>
+        <v>-0.009127945468140284</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.009695511331956251</v>
+        <v>-0.02356125346644587</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0897110169219732</v>
+        <v>-0.06615583034034302</v>
       </c>
       <c r="AP3" t="n">
         <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1703,46 +1703,46 @@
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.005130305055572029</v>
+        <v>-0.09696049762328589</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3590333709403587</v>
+        <v>0.04614453042286838</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.2900985162239982</v>
+        <v>-0.1744856397050651</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.01894844384754438</v>
+        <v>0.008696339820027627</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.004712183066794989</v>
+        <v>0.0009100172694351794</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-1.498422221880701e-11</v>
+        <v>3.102187435372345e-11</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1754,28 +1754,28 @@
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.02193658157874914</v>
+        <v>0.04493162571255065</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.01498747434397339</v>
+        <v>-0.01349577105186921</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2649783619173471</v>
+        <v>0.04088091624097721</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,19 +1784,19 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.02614151671716174</v>
+        <v>-0.1009657637763355</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.2194302533138376</v>
+        <v>0.09518926784970609</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.01783665726270095</v>
+        <v>-0.07513938414180231</v>
       </c>
       <c r="BZ3" t="n">
         <v>-0</v>
@@ -1805,133 +1805,133 @@
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.07150037158550204</v>
+        <v>0.05588315881988896</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.06259949192483927</v>
+        <v>-0.02401809258256586</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.11613646014278</v>
+        <v>0.05428757351465516</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.01442328400586075</v>
+        <v>-0.008501124278512594</v>
       </c>
       <c r="CN3" t="n">
         <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.06211471512727219</v>
+        <v>-0.01141484539553626</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2025347252886558</v>
+        <v>-0.04375700489279372</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.08733507312211922</v>
+        <v>0.04964332458412248</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.04622504245530599</v>
+        <v>-0.03631619246938488</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0727083706734023</v>
+        <v>0.0225650107711955</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.02494491696250728</v>
+        <v>0.03880140975567671</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.001830290917866769</v>
+        <v>0.000617904393682361</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.1078863942329314</v>
+        <v>0.1240512609221929</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.0495112175625067</v>
+        <v>0.05447482776245566</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.06402648134340873</v>
+        <v>0.008178726733314157</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2741129911128643</v>
+        <v>-0.04847371511314432</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -1943,109 +1943,109 @@
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.0560313155278815</v>
+        <v>0.04854207333263161</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.03233832905909581</v>
+        <v>0.0831090016579535</v>
       </c>
       <c r="DZ3" t="n">
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.06831951913934045</v>
+        <v>-0.03444624303256823</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.05692924531423291</v>
+        <v>0.01671392562109603</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.1315344168018623</v>
+        <v>0.0003774945759717391</v>
       </c>
       <c r="EI3" t="n">
         <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0271855568173511</v>
+        <v>0.04978808491395471</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.04447748664650403</v>
+        <v>-0.004408774527572875</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.06925747733293601</v>
+        <v>-0.01214161128273236</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.03979573209276373</v>
+        <v>0.08741801265672046</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.07005065874839615</v>
+        <v>0.05011513794142743</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.04379724584938963</v>
+        <v>-0.03954139835158769</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.0428165185458087</v>
+        <v>0.03244522743928335</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,22 +2054,22 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.04703563934071713</v>
+        <v>0.1438669590016134</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.0230646152790354</v>
+        <v>0.0007892104177395479</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.06775892935197425</v>
+        <v>-0.00305700253183764</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
@@ -2081,19 +2081,19 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.001724701672075878</v>
+        <v>0.1329319096241283</v>
       </c>
       <c r="FQ3" t="n">
         <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.001847322038181296</v>
+        <v>0.001064399228726966</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.009314127950876893</v>
+        <v>0.004450767193539159</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2102,111 +2102,111 @@
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.006657047046876744</v>
+        <v>0.100262548678274</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.009811642038544302</v>
+        <v>-0.005773777391574707</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.09236686947825894</v>
+        <v>0.06004754378587881</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006979808171394947</v>
+        <v>0.007120752380513796</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003761389592882762</v>
+        <v>-0.01036923499517919</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03202485795484759</v>
+        <v>0.02904368128446825</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06430377273454811</v>
+        <v>0.05997553051503294</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0004838967393094731</v>
+        <v>-0.0006116667180203248</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1006833495100969</v>
+        <v>0.02630477608416529</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02658843709637288</v>
+        <v>-0.02207618971323788</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07676168023003926</v>
+        <v>-0.01112579715346282</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
@@ -2218,55 +2218,55 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004918981325629149</v>
+        <v>-0.007343668563746881</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.00157724760736132</v>
+        <v>-0.00856299776242452</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005849440517497382</v>
+        <v>-0.01335878477435961</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01456132103952213</v>
+        <v>0.05429914324887735</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.02883437661307887</v>
+        <v>-0.01841933274502594</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.01413082462982092</v>
+        <v>0.02041568618544967</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.2602372119317341</v>
+        <v>0.1783322801947033</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01583096869341796</v>
+        <v>-0.04305661861959745</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.205443368733909</v>
+        <v>-0.06575559401580923</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,25 +2302,25 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0006629251887094801</v>
+        <v>-0.004938347073081406</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.01189283172273567</v>
+        <v>-0.003661349703346866</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.008302306309810806</v>
+        <v>-0.002703439578519854</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.006772078497978714</v>
+        <v>-0.00785080729083224</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.08257420179638068</v>
+        <v>0.01307764977307723</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02427175354081476</v>
+        <v>0.04369158087558968</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,130 +2356,130 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1550434937347541</v>
+        <v>0.1218247121572249</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01779769611138463</v>
+        <v>-0.03680120618051298</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.04780919508630652</v>
+        <v>-0.0006875982086009832</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.06369467855728035</v>
+        <v>-0.06439383803200559</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-8.298433539816928e-05</v>
+        <v>0.04380202050901179</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.0140853617830723</v>
+        <v>0.007993632876538649</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.00523178455913114</v>
+        <v>-0.03106640340873208</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.05779466917939787</v>
+        <v>0.05435190435620066</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.09988545258876912</v>
+        <v>0.03174477627019047</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.0568760971157278</v>
+        <v>-0.06725042231192499</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02587768132252319</v>
+        <v>0.05050574817979147</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.01132446283934437</v>
+        <v>0.008824112620697672</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.05301988473128048</v>
+        <v>-0.0311456721062643</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.001781537506871868</v>
+        <v>-0.003351297534648582</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.000127301796825691</v>
+        <v>0.0005821749149891081</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,25 +2491,25 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.08225556265504953</v>
+        <v>-0.03483530510772586</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.04798273219268543</v>
+        <v>0.009929779994307037</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.001476332662392453</v>
+        <v>-0.03002857833257226</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,52 +2518,52 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.02720681698109994</v>
+        <v>0.02949057226716126</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.03755984151876449</v>
+        <v>0.03971635608356051</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001416297701204746</v>
+        <v>-0.007278643965650306</v>
       </c>
       <c r="EB4" t="n">
         <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.02012804502901441</v>
+        <v>-0.0499390475683387</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.02462595246815462</v>
+        <v>0.03795159900344369</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.02027342023523696</v>
+        <v>0.01821557564939014</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,103 +2572,103 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.06196133355660624</v>
+        <v>-0.03421123837511522</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.01864422081224564</v>
+        <v>-0.0364712198597615</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.008105509380230882</v>
+        <v>0.007221696888298941</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.06364256283218737</v>
+        <v>-0.07239461099662216</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.01067255492501695</v>
+        <v>0.04633268430262349</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.02278671153849575</v>
+        <v>0.003775771730090378</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.00391853280203546</v>
+        <v>-0.02719687104622487</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.01735307970087306</v>
+        <v>0.004282950539830217</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.01439852800531348</v>
+        <v>0.001677226559852551</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.002251424285415937</v>
+        <v>0.001058753417158744</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.01076519634478988</v>
+        <v>0.06564065058057554</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0002169498138988619</v>
+        <v>-0.0005084899941324605</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.002140847415356864</v>
+        <v>-0.0578740416020929</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02942315284659443</v>
+        <v>0.02166841746058458</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>-0</v>
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01653515410486692</v>
+        <v>0.1500296781201497</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01911390420995132</v>
+        <v>0.03733118526140449</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.008245198928792323</v>
+        <v>-0.03533479202782056</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,52 +2736,52 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002739099093476765</v>
+        <v>0.09859566917754559</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.00797862307411704</v>
+        <v>-0.001398123027897962</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004630358118928467</v>
+        <v>0.02374961465165391</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.00562431451528824</v>
+        <v>0.1137650505373231</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01917650944817647</v>
+        <v>-0.09757741618690459</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01675235631397933</v>
+        <v>0.01661634721355691</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
@@ -2790,34 +2790,34 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.004128973093071418</v>
+        <v>-0.008544770875427182</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.004606771161319813</v>
+        <v>-0.04227485522340275</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.003450040950057821</v>
+        <v>-0.008107044509890244</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01041150882885401</v>
+        <v>0.08548211621631104</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,37 +2826,37 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01065120974628828</v>
+        <v>0.05421460254287308</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.002447436279189523</v>
+        <v>-0.05699811608576565</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.04253967296278888</v>
+        <v>0.3898032720114853</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.03746081538641886</v>
+        <v>-0.1297345400657429</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01716242063633875</v>
+        <v>-0.117900144611825</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2865,58 +2865,58 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.003264508882337005</v>
+        <v>-0.0004334781007689335</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.004476902446668457</v>
+        <v>0.0008356195856917853</v>
       </c>
       <c r="BH5" t="n">
-        <v>-5.042012244790035e-12</v>
+        <v>-2.737075290701278e-11</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03421519796230633</v>
+        <v>-0.003167521569036508</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.009933432133565019</v>
+        <v>0.07624922536052831</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.007935375843004203</v>
+        <v>0.08262105708346892</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0151924951007541</v>
+        <v>0.3239963405798872</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,16 +2934,16 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.01676915133495285</v>
+        <v>-0.0110811820634468</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.007435630086919295</v>
+        <v>-0.07211130776920854</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
@@ -2952,7 +2952,7 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.001586811405195089</v>
+        <v>-0.1137220535676106</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01111724884207095</v>
+        <v>-0.04901976900978415</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01211068458839425</v>
+        <v>0.06692072446201036</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2976,10 +2976,10 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.01225939043027462</v>
+        <v>-0.09202753768001154</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
@@ -2988,25 +2988,25 @@
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.0021089668999979</v>
+        <v>0.03676982837582392</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.006769152191640431</v>
+        <v>0.0256380769301258</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.004156513311446919</v>
+        <v>-0.1014150226031914</v>
       </c>
       <c r="CX5" t="n">
         <v>0</v>
@@ -3015,16 +3015,16 @@
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01049359044323327</v>
+        <v>-0.05537702552418535</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01723393150546558</v>
+        <v>0.06918755714770509</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01362814359458097</v>
+        <v>-0.01712373197329225</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02092423926673847</v>
+        <v>-0.06076599618845245</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.002449107007490194</v>
+        <v>0.007736741455438357</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,31 +3054,31 @@
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.006065422752101692</v>
+        <v>-0.08373146707635319</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.03009324741425295</v>
+        <v>-0.005959084921257882</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.01460990387441181</v>
+        <v>-0.009969418623937727</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,25 +3087,25 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.02033606293362293</v>
+        <v>0.08092080240787711</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02040454557665802</v>
+        <v>-0.05824580864378498</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.004976904989508604</v>
+        <v>0.1012938646395145</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,34 +3114,34 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.002754898865395519</v>
+        <v>-0.006579260025780021</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.006854070602082988</v>
+        <v>-0.0946320635477466</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.008413497337904438</v>
+        <v>-0.01160698138962902</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.01017791791074769</v>
+        <v>-0.05331760990817312</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.01350489936880137</v>
+        <v>-0.140038024393197</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01496493360818805</v>
+        <v>0.0815648136322378</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.008403689172668186</v>
+        <v>-0.1176865880672105</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,43 +3177,43 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.008448832762520129</v>
+        <v>-0.06640334717244117</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01521872835127585</v>
+        <v>0.05107209972954268</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02154077973397725</v>
+        <v>-0.05648081723356498</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.03578232937902517</v>
+        <v>-0.002965698340662393</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0111743478035686</v>
+        <v>0.03235139801448283</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
@@ -3222,34 +3222,34 @@
         <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001272023499250767</v>
+        <v>0.02796211720489261</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0009491870339020724</v>
+        <v>0.003545488796013986</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02495684476485229</v>
+        <v>-0.06784104915042662</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01446470466638105</v>
+        <v>-0.04642146852452791</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3261,10 +3261,10 @@
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.0041381974384793</v>
+        <v>0.02879541520119193</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7531074809582915</v>
+        <v>0.1046240503430633</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1495041690045623</v>
+        <v>-0.0322362078413863</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.008564669282557657</v>
+        <v>-0.01746085965812928</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4032164875041103</v>
+        <v>0.09693069506699267</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04098190157168451</v>
+        <v>0.01273706111855209</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06965048154523779</v>
+        <v>-0.02010308377806195</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3898,79 +3898,79 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2452716294926828</v>
+        <v>0.03478367440014492</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2263666529770736</v>
+        <v>-0.03027589139214292</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.114204589354659</v>
+        <v>-0.03037187567012073</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.07056093538435346</v>
+        <v>-0.005111236841248349</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.03543123241448971</v>
+        <v>-0.01035912390977814</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.003127749518318098</v>
+        <v>-0.01917432471698327</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1587071321945224</v>
+        <v>0.06457878228376651</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1189501206664909</v>
+        <v>-0.02260175879039483</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.09115284634179519</v>
+        <v>0.02498279045696926</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.43274115298841</v>
+        <v>0.210762686080349</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.1455032860242808</v>
+        <v>-0.07935779241478123</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.3951367484564425</v>
+        <v>-0.08503737246393808</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.07807679892086299</v>
+        <v>-0.01292940369691877</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.03636927162022136</v>
+        <v>-0.008256497056630662</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1196293891578984</v>
+        <v>-0.009467336787770357</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,31 +4027,31 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1849368636205873</v>
+        <v>0.001139112263471103</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.3002104136813118</v>
+        <v>0.02260204191170433</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1384816467664778</v>
+        <v>0.05348130887927287</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.7144499124914935</v>
+        <v>0.1471228681285252</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.05875782646525196</v>
+        <v>-0.03337002235688893</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.00343897033086684</v>
+        <v>-0.02119774256107646</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,46 +4090,46 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.3075709651160257</v>
+        <v>-0.06865623965082619</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.07093140580851341</v>
+        <v>0.05570853298304618</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.1080225227916755</v>
+        <v>0.00816308870736142</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.002046742422624026</v>
+        <v>-0.03377051447729319</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.2610973187669751</v>
+        <v>0.05742959173753695</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.2268934900286013</v>
+        <v>0.03195532309346392</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,52 +4138,52 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.2383716554892569</v>
+        <v>-0.07193819376543956</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.170993275764668</v>
+        <v>0.06290597483382644</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.1057934270933668</v>
+        <v>0.01505124963373965</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1281490023899826</v>
+        <v>-0.02261210887413567</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.03387882310809813</v>
+        <v>-0.004735831902576178</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01549401573564813</v>
+        <v>-0.007403846869930247</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4198,19 +4198,19 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.1456251106296911</v>
+        <v>-0.04445964737092536</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.1080617851157746</v>
+        <v>0.01591929222935484</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.0875100703466339</v>
+        <v>-0.03381855950669221</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,22 +4225,22 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.009827912079582229</v>
+        <v>0.0111205682863625</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.1023783661999643</v>
+        <v>0.02982689449185097</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.2454140493372591</v>
+        <v>-0.008994679543972262</v>
       </c>
       <c r="EB7" t="n">
         <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -4249,52 +4249,52 @@
         <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1389715601501559</v>
+        <v>-0.04267323834359386</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07871434507327166</v>
+        <v>0.04994692297249256</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.01893159884896906</v>
+        <v>0.01010112615746054</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.2442104600870094</v>
+        <v>-0.04200675269071617</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.1867940533228023</v>
+        <v>-0.04150394163028932</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.1901227733176786</v>
+        <v>0.00276624798588716</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,46 +4306,46 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.2591103604429765</v>
+        <v>-0.07819758061391528</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.1177038889848845</v>
+        <v>0.05883319974141765</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.1126498888784556</v>
+        <v>0.005834319137208572</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.07060883676866575</v>
+        <v>-0.0461859114504343</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.151885016407868</v>
+        <v>0.01930646190549959</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.1135193599017184</v>
+        <v>0.01750304397082377</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4354,25 +4354,25 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.06789566843294029</v>
+        <v>0.002480725186962475</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.2125064681820947</v>
+        <v>0.10761947461896</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.1719947813321319</v>
+        <v>-0.01435945165811647</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4384,31 +4384,31 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.1326879437481042</v>
+        <v>-0.04966069772927316</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.08762742514024854</v>
+        <v>0.01219986033129244</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4985,25 +4985,25 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.06692013671556604</v>
+        <v>0.1318286361418962</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.007698636910770198</v>
+        <v>0.007817734994164091</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.01526296678998702</v>
+        <v>-0.03517696102108809</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02375884960327811</v>
+        <v>0.1676855329727245</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02137050315071144</v>
+        <v>-0.01776865857029999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01006654873820268</v>
+        <v>0.0136690695234335</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0</v>
@@ -5036,10 +5036,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0009988672468050383</v>
+        <v>0.04030479376347024</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,37 +5048,37 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01745118797245224</v>
+        <v>-0.06092721248345735</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0169785956205028</v>
+        <v>0.02604543077507457</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.004317274279963414</v>
+        <v>-0.0025082137875116</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.007869420444146536</v>
+        <v>-0.02422343590344568</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001009917385144851</v>
+        <v>2.028998180320486e-05</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -5087,13 +5087,13 @@
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01292516747852669</v>
+        <v>0.0656298953568214</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,25 +5102,25 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.009408746994766772</v>
+        <v>0.007537451641716182</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.01465675484797975</v>
+        <v>-0.05488785249186845</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1058366067877649</v>
+        <v>0.3417529928856365</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -5129,52 +5129,52 @@
         <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0082007164108862</v>
+        <v>-0.0715118608064487</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.01673018408105359</v>
+        <v>-0.1007414360251559</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01386038139405156</v>
+        <v>-0.02683617345330867</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.01305096889270698</v>
+        <v>-0.0319026166904537</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.003916014014959461</v>
+        <v>-0.007986276254670261</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.03855135551404824</v>
+        <v>0.01901978263206083</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,16 +5183,16 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.02596299839252248</v>
+        <v>0.09202342486906359</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01363593773567502</v>
+        <v>0.07091375573518559</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -5201,25 +5201,25 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.04160734495829051</v>
+        <v>0.1961805412122276</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.02896190079870664</v>
+        <v>-0.01569918423822938</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.02623374164207505</v>
+        <v>-0.03498834296088231</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.01021121588104703</v>
+        <v>-0.06802884885886072</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.002657907976476829</v>
+        <v>0.006880430614843442</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01703656807997285</v>
+        <v>0.042292731036304</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5252,55 +5252,55 @@
         <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.01464176343024662</v>
+        <v>-0.05193693535965875</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.005383069586818494</v>
+        <v>0.1007911039616115</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.02528367336834453</v>
+        <v>0.004504584074273084</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.004319751624972959</v>
+        <v>-0.06209336860597533</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.0001546267831410483</v>
+        <v>0.007429280782746868</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0220186973712585</v>
+        <v>0.0484200971685799</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,25 +5309,25 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.01093068582250599</v>
+        <v>-0.002726282346296123</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01696039703971827</v>
+        <v>-0.04544014567812261</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01720814075582321</v>
+        <v>0.07869964151386276</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
         <v>0</v>
@@ -5336,22 +5336,22 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.003040710677854332</v>
+        <v>-0.04765778061487626</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.02257622502596876</v>
+        <v>-0.01336474692719589</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.005797130557044341</v>
+        <v>0.02304619884723903</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,25 +5363,25 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.02587838974234904</v>
+        <v>0.002804233365923414</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.04498270796651414</v>
+        <v>-0.1020856110394351</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.01469546633585775</v>
+        <v>0.01578824188802605</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,76 +5390,76 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.001173331975195375</v>
+        <v>-0.0009178727080572242</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.01170680737225634</v>
+        <v>-0.02343257450103831</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.00230608257389561</v>
+        <v>-0.006440112272731733</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.00637155468317768</v>
+        <v>-0.01430083630715559</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.0123611003589092</v>
+        <v>-0.113616538792832</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.05772247863443561</v>
+        <v>-0.1421157210232721</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.000685533797697584</v>
+        <v>-0.07203002191469346</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.0002219075286049679</v>
+        <v>-0.005953772722106577</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.02170245804226252</v>
+        <v>0.03339712365508587</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5471,64 +5471,64 @@
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.0231384710108488</v>
+        <v>-0.08236326848594332</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.05048600306408532</v>
+        <v>0.04376879064877498</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.007131253066648013</v>
+        <v>0.002233441911127721</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0004095146174966913</v>
+        <v>0.02791215368997892</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.01160022670605569</v>
+        <v>0.007625445417755534</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.04196190299251346</v>
+        <v>-0.08084680033485234</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02425752562382387</v>
+        <v>-0.01060100053622391</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.00639797179176058</v>
+        <v>-0.03277063800963731</v>
       </c>
       <c r="GE9" t="n">
         <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1712863114473656</v>
+        <v>0.1751939360811453</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.03796502845542246</v>
+        <v>-0.04845843995259011</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.04737848213212567</v>
+        <v>-0.04459680884214391</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5575,22 +5575,22 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1182888863385793</v>
+        <v>0.1739762052943203</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01192962242350428</v>
+        <v>-0.0218216944881022</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.05944875942275085</v>
+        <v>-0.05621804657388186</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5602,103 +5602,103 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.05722972474486246</v>
+        <v>0.05835698155598177</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01046553216889693</v>
+        <v>-0.02972941975870926</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02808469387429977</v>
+        <v>-0.04233074771208535</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01673929346319286</v>
+        <v>-0.01124794075997898</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.01231485737333374</v>
+        <v>-0.01383591440345973</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001694138348302584</v>
+        <v>-0.02978252408723408</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02034157055315556</v>
+        <v>0.07537594595273256</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.03344262271137145</v>
+        <v>-0.02310169506775687</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.03887131747375178</v>
+        <v>0.0240341027589725</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3183382078861889</v>
+        <v>0.2592735073806272</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.02115433228579579</v>
+        <v>-0.08899717078722982</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1575356266136382</v>
+        <v>-0.1216363731122356</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01079562669345964</v>
+        <v>-0.02345784408096589</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.01612422805532911</v>
+        <v>-0.0088472411692118</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.06610050271055802</v>
+        <v>-0.02072410885121132</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.07054037891642595</v>
+        <v>0.008060441278678282</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.05661358910673901</v>
+        <v>0.03361313906912871</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.09449768741576664</v>
+        <v>0.05008167401097176</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,76 +5770,76 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1634579663398945</v>
+        <v>0.2082224711274827</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.00274819160867778</v>
+        <v>-0.06853882880701484</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.02120236475338493</v>
+        <v>-0.04360727738421191</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.05345852274625645</v>
+        <v>-0.08476578863555369</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.005679547297831632</v>
+        <v>0.07122910644885082</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.005306705878183</v>
+        <v>0.01297770761538995</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.03568702633521963</v>
+        <v>-0.04792545386783361</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.04436266335623708</v>
+        <v>0.06312530850314386</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.08634830961935626</v>
+        <v>0.03616863937696731</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
@@ -5851,49 +5851,49 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.03018420341628278</v>
+        <v>-0.08667842955289698</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0285912201215302</v>
+        <v>0.08050425357776378</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01287203013867217</v>
+        <v>0.02209380492585794</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.04526691187746678</v>
+        <v>-0.07293588807331007</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01258912294407035</v>
+        <v>0.05583086585992706</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.01316545437119579</v>
+        <v>-0.03249922327164721</v>
       </c>
       <c r="DJ10" t="n">
         <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,217 +5905,217 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.03986165864711567</v>
+        <v>-0.04675061875623168</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.05312889245093388</v>
+        <v>0.02436537206116761</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.00752713499362133</v>
+        <v>-0.02426508939670904</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0453389105192584</v>
+        <v>0.02942150923376052</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.05059546115836701</v>
+        <v>0.02919742214260903</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.02849456738785242</v>
+        <v>-0.03114455270633319</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.0270548173741125</v>
+        <v>-0.03524770581849452</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07780448254855828</v>
+        <v>0.06615655836567497</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.05138656114088212</v>
+        <v>0.004922666872664602</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.05515026620620901</v>
+        <v>-0.05714642465155417</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.06399665268745858</v>
+        <v>-0.05492992652875127</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01804349450838135</v>
+        <v>-0.01441429944918136</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.04776032676788616</v>
+        <v>-0.09612575556957431</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01910302737017021</v>
+        <v>0.07718888421405305</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01137434268864248</v>
+        <v>0.01022996850999029</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.04983481055607748</v>
+        <v>-0.05259181342947356</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.05259301818027051</v>
+        <v>0.03989000610859876</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02626979598803915</v>
+        <v>0.01163847501448609</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.01884386494285135</v>
+        <v>0.00585617356857291</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.02202338409996755</v>
+        <v>0.08079600550967206</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.02353331687864172</v>
+        <v>-0.01977914442428499</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.008929060785395973</v>
+        <v>-0.05419834418832242</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.02719958895625641</v>
+        <v>0.01333917475481372</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6692,43 +6692,43 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1967477208947564</v>
+        <v>0.06074873873477344</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.004872265091194075</v>
+        <v>-0.003889759625662089</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.02837682393856376</v>
+        <v>-0.01795134019156774</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.116776944234789</v>
+        <v>0.07401433320454719</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.006951769056264325</v>
+        <v>0.006255222616555193</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.02842913099643884</v>
+        <v>-0.02896193675166796</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,25 +6740,25 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06086784869816914</v>
+        <v>0.02791115061291402</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.02034314225616877</v>
+        <v>-0.01852534914657623</v>
       </c>
       <c r="W12" t="n">
-        <v>0.05035320125856222</v>
+        <v>-0.007212291135012052</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,46 +6770,46 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01267934448369045</v>
+        <v>-0.0007763535266766436</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.002797233796791172</v>
+        <v>-0.009997309870422797</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.003174615656739935</v>
+        <v>-0.006334617336254192</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.0005254745217937639</v>
+        <v>0.02865225080254765</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.01586140385751073</v>
+        <v>-0.004099014277274058</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.02460788336239492</v>
+        <v>0.02879611932217942</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6824,46 +6824,46 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2836599140785776</v>
+        <v>0.103106628234913</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0247045848605295</v>
+        <v>-0.01526153126348673</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08781716397491006</v>
+        <v>-0.05437376472816221</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01926705599221756</v>
+        <v>-0.02171106795569198</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.02768828583778542</v>
+        <v>-0.00138151043378305</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.03735425356236665</v>
+        <v>-0.008436403021960888</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.08426837505918107</v>
+        <v>0.02962891895439955</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0101499845918527</v>
+        <v>0.01097400229585997</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1094836136844937</v>
+        <v>0.03773499739817775</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6908,43 +6908,43 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1420761185347105</v>
+        <v>0.07874500860693298</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0152030182012071</v>
+        <v>-0.03178618245802724</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.03775478345620469</v>
+        <v>-0.01731667489793599</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05586648558837519</v>
+        <v>-0.02599509817344935</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.002971947335261922</v>
+        <v>0.02592973122066764</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.001850693063388636</v>
+        <v>0.01198166808502256</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6956,49 +6956,49 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.03330164037527465</v>
+        <v>-0.03216885445670557</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.03118696582035519</v>
+        <v>0.02374778565324595</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.05820720391161267</v>
+        <v>0.02752999858953947</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03900416094557654</v>
+        <v>-0.02715357645704208</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.008175261877428851</v>
+        <v>0.03169230891224878</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.002528719973443893</v>
+        <v>0.01243395333632475</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7007,28 +7007,28 @@
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.01336814134607777</v>
+        <v>0.002006773222763457</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03268254201884994</v>
+        <v>0.008751862623341699</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.005690566030630777</v>
+        <v>-0.004074210643828254</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7040,73 +7040,73 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06801742044870897</v>
+        <v>-0.02897721219882668</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.01833799856181818</v>
+        <v>-0.02196687112483586</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.006270177971182392</v>
+        <v>-0.02243480303804125</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.006914874914832961</v>
+        <v>0.03954358244318998</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.01770957462388867</v>
+        <v>0.01534594124036323</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.02682832782717445</v>
+        <v>-0.04256685891871886</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03187961122065148</v>
+        <v>-0.0002939312962154249</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.006586336872955008</v>
+        <v>0.01854508542456964</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.02700006138957949</v>
+        <v>0.02562904105665485</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,7 +7115,7 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,25 +7124,25 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.04093468309117096</v>
+        <v>-0.003390772540662928</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0.006741975655173421</v>
+        <v>0.01929360496863816</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02487739632918624</v>
+        <v>0.005850265767029958</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,16 +7151,16 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.04196201217797101</v>
+        <v>-0.03127926856299725</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.002227011316701669</v>
+        <v>0.03558985718803918</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01594024624359943</v>
+        <v>0.008309137068756431</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7175,55 +7175,55 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0208388691368058</v>
+        <v>0.004855684571395597</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01883390333143351</v>
+        <v>0.009468266321568697</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01293236814637832</v>
+        <v>-0.02501411470254545</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.04618970860674082</v>
+        <v>0.01800369687857918</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.03594314514803253</v>
+        <v>0.03589261280069899</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.001185876646727552</v>
+        <v>-0.04554940163557047</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
@@ -7232,28 +7232,28 @@
         <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.00385376722799897</v>
+        <v>0.001132351990417148</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.03462309383010512</v>
+        <v>0.0003829393575601626</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,22 +7261,22 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.195493801821271</v>
+        <v>0.1046992717232178</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.00262433643965683</v>
+        <v>-0.04380932874742949</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1123130265949508</v>
+        <v>-0.04410650431527321</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1460540106776211</v>
+        <v>0.1666447642936649</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01281029644780225</v>
+        <v>-0.07924692196547506</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.08690718197286153</v>
+        <v>-0.02979805461192514</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.009516749568929046</v>
+        <v>0.0351392995173556</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,25 +7324,25 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.04213149074306444</v>
+        <v>-0.01367486628839358</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.00875229422033265</v>
+        <v>-0.005739543346307549</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01537375536667186</v>
+        <v>-0.003444705547117668</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -7351,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.008969460895326143</v>
+        <v>-0.02312185662913138</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.001075567528596065</v>
+        <v>-0.00102528233912652</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,28 +7363,28 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01919028624154192</v>
+        <v>0.03193528172724642</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.02452725996030964</v>
+        <v>0.01200728559440222</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.04685764606827698</v>
+        <v>-0.01880411520178354</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,37 +7393,37 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2037734641204624</v>
+        <v>0.1668890881735769</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01646481092004047</v>
+        <v>-0.0754436014311024</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.103121402873532</v>
+        <v>-0.05637709753255934</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.05836311109248396</v>
+        <v>-0.008022095506493455</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.03041243685794306</v>
+        <v>-0.03756703162716841</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.02888214728328173</v>
+        <v>-0.02008574291188483</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.08977949986049211</v>
+        <v>0.03281655123404687</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,25 +7459,25 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.04281419079574032</v>
+        <v>0.05111702287706049</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01313708953238299</v>
+        <v>0.002356341240437258</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.09209549202766351</v>
+        <v>0.1474744849876853</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.02465785465065819</v>
+        <v>-0.02261716358808872</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.0188113852500117</v>
+        <v>-0.02616283810160829</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7504,46 +7504,46 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.04754226287899155</v>
+        <v>-0.05297950397524855</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.0103755135045273</v>
+        <v>0.02398914840284505</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.03834580492435055</v>
+        <v>0.04127941148886242</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
       </c>
       <c r="CK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.01345214999114164</v>
+        <v>-0.1003224623350294</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.02039721178057041</v>
+        <v>0.05915831845344691</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.0417184007410606</v>
+        <v>0.05184194605045334</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7552,79 +7552,79 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.03213678433521184</v>
+        <v>-0.04515409070243256</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.009805329673056182</v>
+        <v>0.0198695842419276</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.038022920070216</v>
+        <v>0.04065539289836598</v>
       </c>
       <c r="DB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.00622528152549361</v>
+        <v>0.0002946167042541655</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.003569384862801263</v>
+        <v>-0.01384719780604454</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-3.222820901262594e-05</v>
+        <v>0.014210996200159</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.02169473200569216</v>
+        <v>-0.04143458340804888</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03408508832012905</v>
+        <v>0.01900951846392074</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.004170221164915911</v>
+        <v>-0.03140237787612263</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
@@ -7633,13 +7633,13 @@
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01486740590448314</v>
+        <v>0.02804286185500048</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,13 +7648,13 @@
         <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.03673486163849918</v>
+        <v>-0.01078813776041749</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01248081776169925</v>
+        <v>-0.08906677824958563</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
@@ -7666,7 +7666,7 @@
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02300870499644768</v>
+        <v>0.01751863618404378</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,37 +7675,37 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.005710237687450103</v>
+        <v>0.001099032940967893</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.02927829074474437</v>
+        <v>0.02885877517086386</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.03876350886544885</v>
+        <v>-0.02528451282232739</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.02989406189698851</v>
+        <v>-0.02020284008772543</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.06878887911503173</v>
+        <v>0.04003041067051415</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
@@ -7714,31 +7714,31 @@
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.03254807243068258</v>
+        <v>-0.05727337506206529</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.007394094081075812</v>
+        <v>0.0130671036885425</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.04177928752133848</v>
+        <v>0.03717234128156535</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
         <v>-0</v>
@@ -7747,7 +7747,7 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.01453961554677161</v>
+        <v>-0.04252202547318758</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,37 +7756,37 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.04340098043238874</v>
+        <v>0.02399432189243665</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02043022316993903</v>
+        <v>0.005491935027898105</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01959464406170035</v>
+        <v>0.02414767283404416</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.02390750666654722</v>
+        <v>-0.0455298128044691</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.002320044599917166</v>
+        <v>0.0004942518367445441</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,13 +7795,13 @@
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.03007550638754577</v>
+        <v>0.001245589930916076</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.02909638141826818</v>
+        <v>0.001197721161351397</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7833,13 +7833,13 @@
         <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.07456227594869803</v>
+        <v>-0.02241409194984206</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2262579093387404</v>
+        <v>0.02763679243337344</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.07668622950747261</v>
+        <v>-0.04655912773761502</v>
       </c>
       <c r="F14" t="n">
         <v>-0</v>
@@ -7848,25 +7848,25 @@
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
         <v>-0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
         <v>-0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.09035003424277582</v>
+        <v>-0.02331029320056025</v>
       </c>
       <c r="M14" t="n">
-        <v>0.260863098418725</v>
+        <v>0.02035156450412963</v>
       </c>
       <c r="N14" t="n">
-        <v>0.04626602657923398</v>
+        <v>-0.04457984530414748</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
@@ -7875,25 +7875,25 @@
         <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.05559316916798959</v>
+        <v>-0.01042021354461238</v>
       </c>
       <c r="V14" t="n">
-        <v>0.07592653641401946</v>
+        <v>0.03576714197409259</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01854353142418418</v>
+        <v>0.008469050832594402</v>
       </c>
       <c r="X14" t="n">
         <v>-0</v>
@@ -7902,10 +7902,10 @@
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -7914,13 +7914,13 @@
         <v>-0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.009771008800622056</v>
+        <v>-0.0083753897303766</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01585153559192339</v>
+        <v>-0.0117488241882012</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.02190327240067729</v>
+        <v>-0.01413764935431492</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
@@ -7938,43 +7938,43 @@
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.009423533362920684</v>
+        <v>-0.02516497451196773</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.02590354781923845</v>
+        <v>0.02898185254726592</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.03430777962838209</v>
+        <v>-0.01063515395202387</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.09583536249624817</v>
+        <v>-0.04415671490823063</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1786988405945926</v>
+        <v>0.0997802213891647</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.1862591724634094</v>
+        <v>-0.0829959530493093</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -7995,13 +7995,13 @@
         <v>-0</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.02051622049852461</v>
+        <v>0.0008814114473619391</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.05141479207832069</v>
+        <v>-0.08155054850815077</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.03123479940405085</v>
+        <v>-0.03943867004981953</v>
       </c>
       <c r="BH14" t="n">
         <v>-0</v>
@@ -8010,25 +8010,25 @@
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0556334881966089</v>
+        <v>0.02686907144603846</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0024377403277938</v>
+        <v>0.04567472828132278</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.1521009055218665</v>
+        <v>0.05805410443246959</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -8037,115 +8037,115 @@
         <v>-0</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0.1046079441190873</v>
+        <v>-0.03860128416305073</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.1162344249057741</v>
+        <v>0.105307879039335</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.121759208039611</v>
+        <v>-0.02062829455514074</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.05785254690421136</v>
+        <v>0.02801664753842099</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.0604513139156312</v>
+        <v>0.005188006044693146</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01083007273344436</v>
+        <v>0.00997213218549845</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.007496658827611843</v>
+        <v>0.005059132193539757</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.007517122919148013</v>
+        <v>0.03079069968463233</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.06862229069512946</v>
+        <v>0.05283946302255259</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
         <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.03874822412503003</v>
+        <v>0.02079037349965204</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.05054640642885559</v>
+        <v>0.004271185150936057</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01714340891396561</v>
+        <v>0.01726572550443426</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>-0</v>
@@ -8154,19 +8154,19 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0.002967559385418131</v>
+        <v>0.01309918661658499</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.06425750300090968</v>
+        <v>-0.02546235286568098</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.01327898343284288</v>
+        <v>-0.0001286543994519732</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8178,19 +8178,19 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.05421283440306532</v>
+        <v>0.005136205711129674</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.03686665987384669</v>
+        <v>-0.008328679176376802</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.07737948733128533</v>
+        <v>0.02923354851625552</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
@@ -8199,34 +8199,34 @@
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
         <v>-0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.02995790768705678</v>
+        <v>-0.02265161384396748</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.03008075542337652</v>
+        <v>-0.0185890423722036</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.03466597758124259</v>
+        <v>-0.02831012231804675</v>
       </c>
       <c r="EB14" t="n">
         <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE14" t="n">
         <v>0</v>
@@ -8235,22 +8235,22 @@
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.07115265413713048</v>
+        <v>0.002852775604572641</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.06640823691001121</v>
+        <v>0.0214786795011148</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.03575537329969117</v>
+        <v>-0.006739442564019357</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,100 +8259,100 @@
         <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.03498016407504083</v>
+        <v>-0.007471725624693824</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.05257315105408347</v>
+        <v>-0.01454428703028304</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.009346332934057594</v>
+        <v>0.01154783947509741</v>
       </c>
       <c r="ET14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
         <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.05282155879327256</v>
+        <v>0.02154800431041581</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.05867476285528651</v>
+        <v>-0.00566946699457441</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.01632933115529235</v>
+        <v>0.01172408586757103</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.02886968456677217</v>
+        <v>0.03472482244414408</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.04937580179927734</v>
+        <v>-0.009843483220247419</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.05844046550326075</v>
+        <v>-0.03367670443191965</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.006638897624860193</v>
+        <v>-0.001056437208653287</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.005312047427562369</v>
+        <v>0.004295868555555447</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.02022737146092662</v>
+        <v>0.0252730698592184</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8361,22 +8361,22 @@
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.02143107561313182</v>
+        <v>0.01897765326443534</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.03730930171103044</v>
+        <v>-0.04353452908820719</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
@@ -8388,10 +8388,10 @@
         <v>0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -8965,22 +8965,22 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2039042032380843</v>
+        <v>0.1624890108280126</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1794651428754679</v>
+        <v>-0.03517353042275206</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.05426417571395763</v>
+        <v>-0.05604130088587556</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
@@ -8992,37 +8992,37 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1497077258600152</v>
+        <v>0.251104519025754</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1813129142142397</v>
+        <v>-0.0710675130666631</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.06132786598334804</v>
+        <v>-0.05180892514067065</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.04693461228322</v>
+        <v>0.06317744510012414</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,25 +9031,25 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.02371370407454441</v>
+        <v>-0.06460317993792435</v>
       </c>
       <c r="X16" t="n">
-        <v>0.04871372225115689</v>
+        <v>0.009747609914780613</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.02749954987435061</v>
+        <v>-0.02207181338370546</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
@@ -9058,10 +9058,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0005362738560554806</v>
+        <v>-0.06379687752442272</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.008605049747437407</v>
+        <v>0.005166607419836569</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9073,136 +9073,136 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.04732359225231512</v>
+        <v>0.01398072897990404</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01548276700525104</v>
+        <v>-0.04570248291524239</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01970076137404788</v>
+        <v>-0.0225867306381499</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.2141488937998984</v>
+        <v>0.290264670291465</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.1062261028739671</v>
+        <v>-0.1324265044963237</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.0451446279529856</v>
+        <v>-0.07959845254784892</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.05173649375456642</v>
+        <v>-0.0359667448786388</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1070129495180789</v>
+        <v>-0.03791549588927695</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.02067427852827511</v>
+        <v>7.913141324252069e-05</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.08977216179274879</v>
+        <v>0.07754645520822853</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.02566454218381968</v>
+        <v>0.08519851442063854</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.04807652347252042</v>
+        <v>0.03242034364106194</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1301914605638603</v>
+        <v>0.1781957025448215</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.04762874876486222</v>
+        <v>-0.05258211270698402</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0258906902271311</v>
+        <v>-0.02047873662083436</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
         <v>-0</v>
@@ -9211,25 +9211,25 @@
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.03271780498461448</v>
+        <v>-0.05942179253702937</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.03436311909200391</v>
+        <v>0.03381907415401052</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02375783740825914</v>
+        <v>0.02664697909378639</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL16" t="n">
         <v>-0</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.0214513098871394</v>
+        <v>-0.1095875978177684</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,10 +9247,10 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.002208518665768379</v>
+        <v>0.09992244601688334</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.01472796541548929</v>
+        <v>0.002968648043976293</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9265,19 +9265,19 @@
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.01641976526971575</v>
+        <v>-0.05299859485398353</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.03299875652722398</v>
+        <v>0.01309326307506909</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03151716845135254</v>
+        <v>0.03109656387711999</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9289,49 +9289,49 @@
         <v>0</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.0356052353063743</v>
+        <v>-0.04695873188998312</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.02272898681069823</v>
+        <v>-0.02266218589266791</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.004597759484357604</v>
+        <v>-0.01872345834203331</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.02801827752347907</v>
+        <v>-0.02205557932194702</v>
       </c>
       <c r="DP16" t="n">
         <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01870892383402612</v>
+        <v>-0.008257323406525808</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.06810005201429935</v>
+        <v>-0.01853215109101155</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9343,10 +9343,10 @@
         <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.005347577098407808</v>
+        <v>0.03457488949925407</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
@@ -9355,37 +9355,37 @@
         <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.05718706211650888</v>
+        <v>-0.02212621060065236</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.04963009826079739</v>
+        <v>0.001631842142773033</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.01647437049456156</v>
+        <v>-0.007891310834109291</v>
       </c>
       <c r="EH16" t="n">
         <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.03164526663203931</v>
+        <v>-0.009021288163095791</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.007830312550541641</v>
+        <v>0.03635594799454477</v>
       </c>
       <c r="EL16" t="n">
         <v>-0</v>
@@ -9394,58 +9394,58 @@
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.02871633323905612</v>
+        <v>0.001633944621082099</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.01290487038339589</v>
+        <v>-0.04731795650667259</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.04759833445654382</v>
+        <v>0.02004377189911824</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW16" t="n">
         <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.0124994363199761</v>
+        <v>-0.06691307413105145</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.0288083656907957</v>
+        <v>0.02049436982140813</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.03555749521189096</v>
+        <v>0.01932702515407583</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF16" t="n">
         <v>-0</v>
@@ -9454,7 +9454,7 @@
         <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.03770862458792774</v>
+        <v>-0.05458349219990931</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,16 +9463,16 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.03748858524174518</v>
+        <v>0.08250773167892646</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.02218923871449233</v>
+        <v>-0.01045535086384923</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.006739213473433409</v>
+        <v>0.005831272045879421</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,37 +9490,37 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.00412104259029083</v>
+        <v>-0.01598819193376091</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.001489320649345486</v>
+        <v>-0.01814803208195101</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.02977210585132421</v>
+        <v>-0.06225193092248942</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.04201092091254649</v>
+        <v>0.03612388095777556</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
@@ -9537,16 +9537,16 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5551579428259135</v>
+        <v>0.4423443329987101</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2425430702317883</v>
+        <v>-0.2232751408864951</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1506766661926395</v>
+        <v>-0.01990668329270999</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -9564,16 +9564,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4777254912241717</v>
+        <v>0.4940617823599897</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.254909955795878</v>
+        <v>-0.2808597214952874</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2057176965143236</v>
+        <v>-0.05937111514528649</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9591,52 +9591,52 @@
         <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1525492886119854</v>
+        <v>0.1259770771762188</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.008696073752571903</v>
+        <v>-0.06181921781562294</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0861569961346406</v>
+        <v>-0.09541527577831091</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1166096908266328</v>
+        <v>-0.06933896838975366</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.001190052743659858</v>
+        <v>-0.09074958759991542</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.001429558295255545</v>
+        <v>-0.08768311783926977</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
@@ -9645,22 +9645,22 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.06626318813998347</v>
+        <v>0.1255236326289956</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.02260921176166639</v>
+        <v>-0.08301526888939309</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.02537188921776616</v>
+        <v>0.05179515851053841</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,46 +9669,46 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.4988829689007592</v>
+        <v>0.4192209481416405</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0.02192413533171946</v>
+        <v>-0.1333158088145006</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.08879036613131305</v>
+        <v>-0.1843462618513573</v>
       </c>
       <c r="AY17" t="n">
         <v>-0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.06562038319081129</v>
+        <v>-0.004957123426739756</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.09884545298573308</v>
+        <v>-0.06465157051768569</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.2465476722483913</v>
+        <v>-0.05184017953384308</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
@@ -9717,7 +9717,7 @@
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,22 +9726,22 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.06642904013177818</v>
+        <v>-0.04681740816627369</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.05582315380179269</v>
+        <v>-0.001368661349878034</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.04271239389614757</v>
+        <v>0.07219415775121923</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
@@ -9753,19 +9753,19 @@
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.2827111139446433</v>
+        <v>0.3445311867046899</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0.06134877768279721</v>
+        <v>-0.1688681804601636</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.06588681329246723</v>
+        <v>-0.05545085961268199</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9780,46 +9780,46 @@
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.1220913929187614</v>
+        <v>-0.1523844101892461</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.03644679041433904</v>
+        <v>0.1418315563514078</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.01216098720746076</v>
+        <v>0.008387757785333226</v>
       </c>
       <c r="CI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.03532412798487509</v>
+        <v>-0.1667370657215068</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.07588559657295625</v>
+        <v>0.2545750530719122</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.1131815626625403</v>
+        <v>0.1203537279962039</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9828,28 +9828,28 @@
         <v>-0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.1039860629432535</v>
+        <v>-0.1381279837482322</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.05144575046327381</v>
+        <v>0.1463450739232324</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.01250496669015023</v>
+        <v>0.01195160837619561</v>
       </c>
       <c r="DA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
@@ -9861,19 +9861,19 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.07075867959655732</v>
+        <v>-0.1314114159986926</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.03148961340718454</v>
+        <v>0.02420388734106395</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.01798594684873402</v>
+        <v>-0.0898173256911478</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
@@ -9882,25 +9882,25 @@
         <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN17" t="n">
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.05655329607467577</v>
+        <v>-0.0795805007774549</v>
       </c>
       <c r="DP17" t="n">
         <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0.02918312602971489</v>
+        <v>0.08988818165920079</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.08227551019326146</v>
+        <v>-0.006010251962161577</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
@@ -9912,25 +9912,25 @@
         <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.04459618323733418</v>
+        <v>0.04410871229525919</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.03955622728033572</v>
+        <v>-0.05921412088150095</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.02104676492265019</v>
+        <v>0.04570852568851878</v>
       </c>
       <c r="EB17" t="n">
         <v>0</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
@@ -9939,52 +9939,52 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.06839024974759757</v>
+        <v>-0.110974284318262</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.0560507957411942</v>
+        <v>0.07416703795162087</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0659823016708551</v>
+        <v>0.05288973202695449</v>
       </c>
       <c r="EK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.1006079381575802</v>
+        <v>-0.06263967236961035</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.02445448079862796</v>
+        <v>0.06990386406897137</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.03830189902495351</v>
+        <v>-0.04341758257134812</v>
       </c>
       <c r="ET17" t="n">
         <v>-0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9993,112 +9993,112 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.1116252403370809</v>
+        <v>-0.1649794554710959</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.06326882975589</v>
+        <v>0.1542467258594135</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.0152529581331342</v>
+        <v>-4.789192131773617e-05</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.01762596276331823</v>
+        <v>-0.1166830060267382</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.0819593933575707</v>
+        <v>0.1062579569861482</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.0535140285861791</v>
+        <v>0.0333950183918576</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
         <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.004948100312100984</v>
+        <v>0.00426830910897864</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.04945673482434494</v>
+        <v>0.06265515741012269</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.00984892657875802</v>
+        <v>-0.02060378258508473</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX17" t="n">
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.01866325265970753</v>
+        <v>-0.1578758401997867</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.05540680771825736</v>
+        <v>0.04961188042175001</v>
       </c>
       <c r="GC17" t="n">
         <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10106,22 +10106,22 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.136454222055864</v>
+        <v>0.3605316616461264</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01528479203520033</v>
+        <v>-0.01284740306534163</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.08468305517941427</v>
+        <v>-0.110953687967528</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
@@ -10133,52 +10133,52 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1089476941873885</v>
+        <v>0.5180347744570374</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.02157995454045</v>
+        <v>-0.0842369250711098</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1012959849445551</v>
+        <v>-0.09536055722643852</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01872221616371819</v>
+        <v>0.06216301414393695</v>
       </c>
       <c r="U18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.005072572643909984</v>
+        <v>-0.05124289829321659</v>
       </c>
       <c r="X18" t="n">
-        <v>0.007851978048001527</v>
+        <v>0.005150877943904208</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -10187,22 +10187,22 @@
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.01464733222069297</v>
+        <v>0.006257682138970258</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.01284472708252207</v>
+        <v>-0.1120400123653476</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.002308036015302659</v>
+        <v>-0.0480472664726933</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI18" t="n">
         <v>-0</v>
@@ -10214,22 +10214,22 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.00639893919951408</v>
+        <v>0.02536720034174513</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.0130531379601332</v>
+        <v>-0.00422816990229901</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.0149756465026066</v>
+        <v>-0.02665948514664977</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10238,10 +10238,10 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1031832290450098</v>
+        <v>0.3585789156559056</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
@@ -10250,16 +10250,16 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.01526129238740877</v>
+        <v>-0.1246385541750601</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.03789654662286067</v>
+        <v>-0.05282115130978305</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>0</v>
@@ -10268,61 +10268,61 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.04390811816356971</v>
+        <v>0.04815836152598382</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.03211105380045551</v>
+        <v>-0.05578988044105449</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.04650633974858079</v>
+        <v>-0.07714501346013342</v>
       </c>
       <c r="BI18" t="n">
         <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.04528505161976266</v>
+        <v>0.03570243182655668</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.02344144052568435</v>
+        <v>0.06323935324568593</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.008309391879694445</v>
+        <v>-0.008505316151361547</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT18" t="n">
         <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.04833610311662011</v>
+        <v>0.2503983350289534</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.0009560583832833554</v>
+        <v>-0.02593598838194241</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.01669313514946856</v>
+        <v>-0.04117606360932714</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10349,7 +10349,7 @@
         <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.02681092253782091</v>
+        <v>-0.1178929238985295</v>
       </c>
       <c r="CF18" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.002923169881238457</v>
+        <v>0.0127405524959386</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.02506784366970084</v>
+        <v>0.05771824469792567</v>
       </c>
       <c r="CJ18" t="n">
         <v>0</v>
@@ -10370,40 +10370,40 @@
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.01527299122647187</v>
+        <v>-0.1993297310883153</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.009944480840403223</v>
+        <v>0.09529942226810668</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.009173798030434428</v>
+        <v>0.06048926687668136</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.01836816759632294</v>
+        <v>-0.1235158221573166</v>
       </c>
       <c r="CX18" t="n">
         <v>-0</v>
@@ -10412,13 +10412,13 @@
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.002142826162358466</v>
+        <v>-0.006394246611462298</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.02463259027486274</v>
+        <v>0.05543846617383827</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
         <v>-0</v>
@@ -10427,22 +10427,22 @@
         <v>0</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.026956217337294</v>
+        <v>-0.0593641715983156</v>
       </c>
       <c r="DG18" t="n">
         <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.01298530849747217</v>
+        <v>-0.1250744210721377</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.0002284061077876941</v>
+        <v>0.01824883729584411</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10451,52 +10451,52 @@
         <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.01922440472735903</v>
+        <v>-0.09438123934199918</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.006791455569243831</v>
+        <v>0.03731298564502118</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.006902419930850502</v>
+        <v>-0.02155982692067258</v>
       </c>
       <c r="DT18" t="n">
         <v>0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW18" t="n">
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.01348873540882265</v>
+        <v>0.00228021147270243</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.004748662227946882</v>
+        <v>0.09361861404095849</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.01418617198553473</v>
+        <v>-0.06932313264343515</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
@@ -10505,52 +10505,52 @@
         <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
         <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.01226905121920143</v>
+        <v>-0.03561105621120701</v>
       </c>
       <c r="EH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI18" t="n">
         <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.0005463698619766715</v>
+        <v>-0.01984834534004597</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.01482679483973342</v>
+        <v>0.03963272240465405</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.005940816257268848</v>
+        <v>-0.02330301860013907</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.006240349599943447</v>
+        <v>-0.07988897508545831</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.0129354837231548</v>
+        <v>0.08315549351913573</v>
       </c>
       <c r="EU18" t="n">
         <v>-0</v>
@@ -10565,34 +10565,34 @@
         <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.01919260667582262</v>
+        <v>-0.1375034013541365</v>
       </c>
       <c r="EZ18" t="n">
         <v>0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.0002256536348331041</v>
+        <v>-0.0129570849998465</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.02780826921091565</v>
+        <v>0.05310948093974181</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.002984358126909825</v>
+        <v>-0.152353588648952</v>
       </c>
       <c r="FI18" t="n">
         <v>-0</v>
@@ -10601,37 +10601,37 @@
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.01858710004204234</v>
+        <v>0.1025089305317037</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.02192096250131277</v>
+        <v>0.02214332624441886</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
         <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>5.725937803713366e-05</v>
+        <v>0.0007638882414780828</v>
       </c>
       <c r="FR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.001414697908836521</v>
+        <v>-0.007398906028835106</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.01575460842636233</v>
+        <v>-0.01872508091005732</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
@@ -10640,25 +10640,25 @@
         <v>-0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.01520087879327517</v>
+        <v>-0.04541710459263681</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.01857872799264919</v>
+        <v>0.0002341058744626497</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
@@ -10667,7 +10667,7 @@
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10675,16 +10675,16 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9693096854668491</v>
+        <v>0.7997936115904558</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.414675274672283</v>
+        <v>-0.4003713773713442</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2682886518033066</v>
+        <v>-0.1533487514313452</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -10702,19 +10702,19 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7343668891176016</v>
+        <v>0.9119030536722249</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3644393913505021</v>
+        <v>-0.5692066855961579</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.289443778789033</v>
+        <v>-0.2957149691399154</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P19" t="n">
         <v>-0</v>
@@ -10726,55 +10726,55 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2118320877873702</v>
+        <v>0.1506177262971102</v>
       </c>
       <c r="U19" t="n">
         <v>-0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0888531010048189</v>
+        <v>-0.1695759977231388</v>
       </c>
       <c r="W19" t="n">
-        <v>0.009130579721479948</v>
+        <v>-0.212172803416647</v>
       </c>
       <c r="X19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1137264690819172</v>
+        <v>0.001928085068011257</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.02013651303936857</v>
+        <v>-0.1797241012655184</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.008521876979631497</v>
+        <v>-0.185295803367862</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
@@ -10783,16 +10783,16 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.08071388162229773</v>
+        <v>0.2080241003566958</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.05127142038260828</v>
+        <v>-0.1323024722898084</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.06175644199115229</v>
+        <v>0.04887236943983334</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
@@ -10807,46 +10807,46 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.7417093965057329</v>
+        <v>0.8747457731009413</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
       </c>
       <c r="AW19" t="n">
-        <v>-0.01503161150749968</v>
+        <v>-0.2348523816039933</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.02440720705154856</v>
+        <v>-0.4052181549589929</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.1052567486186746</v>
+        <v>-0.06092860633472751</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-0.1865210749118863</v>
+        <v>-0.09414108636086042</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.3760090502094713</v>
+        <v>-0.0646662490406308</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
@@ -10855,7 +10855,7 @@
         <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
@@ -10864,22 +10864,22 @@
         <v>-0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.1565975580897339</v>
+        <v>0.02938779206685446</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.06179874494520846</v>
+        <v>0.01503403923132088</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.1239228739715702</v>
+        <v>0.1623669560349012</v>
       </c>
       <c r="BQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>-0</v>
@@ -10888,22 +10888,22 @@
         <v>-0</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.3955293595488003</v>
+        <v>0.5722824584571561</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX19" t="n">
-        <v>-0.02155269506594122</v>
+        <v>-0.3107704285926533</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.02849283945573523</v>
+        <v>-0.1859850006969775</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
@@ -10918,46 +10918,46 @@
         <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.1835963516252771</v>
+        <v>-0.2775415392177662</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.06030512554844031</v>
+        <v>0.2042467027310005</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.02551290077223061</v>
+        <v>0.06929566519542713</v>
       </c>
       <c r="CI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>0.001556453858324508</v>
+        <v>-0.3487827263250354</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>-0.1459254453048237</v>
+        <v>0.4134855149783538</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.1339840504658734</v>
+        <v>0.1642528823872585</v>
       </c>
       <c r="CR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS19" t="n">
         <v>-0</v>
@@ -10966,55 +10966,55 @@
         <v>-0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
         <v>0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.1572876102234378</v>
+        <v>-0.252625799000019</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
-        <v>0.09613443436881514</v>
+        <v>0.238268848725535</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.03870381335905678</v>
+        <v>0.05357857026306774</v>
       </c>
       <c r="DA19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
         <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.1404095338064327</v>
+        <v>-0.1256689688668694</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.08827306973852397</v>
+        <v>0.04596548117232043</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.01543273145985332</v>
+        <v>-0.1708829102411184</v>
       </c>
       <c r="DJ19" t="n">
         <v>-0</v>
       </c>
       <c r="DK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
@@ -11026,19 +11026,19 @@
         <v>-0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.1045336833343151</v>
+        <v>-0.1578549275072562</v>
       </c>
       <c r="DP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>-0.002345394654317209</v>
+        <v>-0.05379538761471944</v>
       </c>
       <c r="DR19" t="n">
-        <v>-0.09222144553638345</v>
+        <v>-0.03048570124575328</v>
       </c>
       <c r="DS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
@@ -11053,76 +11053,76 @@
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>0.03163902942798742</v>
+        <v>0.1243106925811811</v>
       </c>
       <c r="DY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>0.01835674355994654</v>
+        <v>0.08981623920520684</v>
       </c>
       <c r="EA19" t="n">
-        <v>-0.08090852051140933</v>
+        <v>-0.05491521720269814</v>
       </c>
       <c r="EB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED19" t="n">
         <v>0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.1307233619536361</v>
+        <v>-0.1362090235997583</v>
       </c>
       <c r="EH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0.03835097248113387</v>
+        <v>0.1452022841885748</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.09820357336693178</v>
+        <v>0.07886573034130145</v>
       </c>
       <c r="EK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.09164091844584768</v>
+        <v>-0.09008985698902552</v>
       </c>
       <c r="EQ19" t="n">
         <v>0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0.06763640335692937</v>
+        <v>0.1323593651724974</v>
       </c>
       <c r="ES19" t="n">
-        <v>-0.03160469169765504</v>
+        <v>-0.1019439829667469</v>
       </c>
       <c r="ET19" t="n">
         <v>-0</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
         <v>0</v>
@@ -11131,46 +11131,46 @@
         <v>-0</v>
       </c>
       <c r="EX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.1538507231510892</v>
+        <v>-0.2967891440893436</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
-        <v>0.08224693608845234</v>
+        <v>0.2473844903794488</v>
       </c>
       <c r="FB19" t="n">
-        <v>-0.02425122472207305</v>
+        <v>0.03275859659581886</v>
       </c>
       <c r="FC19" t="n">
         <v>-0</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>0</v>
       </c>
       <c r="FF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG19" t="n">
         <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.05653952438804526</v>
+        <v>-0.1763714346484337</v>
       </c>
       <c r="FI19" t="n">
         <v>-0</v>
       </c>
       <c r="FJ19" t="n">
-        <v>0.09494218578565053</v>
+        <v>0.2002410250165741</v>
       </c>
       <c r="FK19" t="n">
-        <v>-0.06600224145768117</v>
+        <v>0.08126230147696298</v>
       </c>
       <c r="FL19" t="n">
         <v>-0</v>
@@ -11179,25 +11179,25 @@
         <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>0.0001499803669970135</v>
+        <v>0.001213216318233477</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
-        <v>0.04276450373537638</v>
+        <v>0.2352811086939256</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.002101005018160105</v>
+        <v>-0.008500845948620099</v>
       </c>
       <c r="FU19" t="n">
         <v>-0</v>
@@ -11212,31 +11212,31 @@
         <v>0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.02303666037637804</v>
+        <v>-0.2208798891720963</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>-0.03266810648691743</v>
+        <v>0.1266662222797779</v>
       </c>
       <c r="GC19" t="n">
         <v>0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE19" t="n">
         <v>-0</v>
       </c>
       <c r="GF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -11244,19 +11244,19 @@
         <v>-0</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.3584263355158025</v>
+        <v>-0.2509767112384328</v>
       </c>
       <c r="C20" t="n">
         <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07054356519492137</v>
+        <v>-0.005712313160048556</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6757335966407643</v>
+        <v>0.4890093782623005</v>
       </c>
       <c r="G20" t="n">
         <v>-0</v>
@@ -11271,19 +11271,19 @@
         <v>-0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2815249635663052</v>
+        <v>-0.3242079842320448</v>
       </c>
       <c r="L20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>-0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.001076001667134229</v>
+        <v>0.1315558227602506</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6621296652004959</v>
+        <v>0.4977560517456547</v>
       </c>
       <c r="P20" t="n">
         <v>-0</v>
@@ -11298,19 +11298,19 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.02261152973827276</v>
+        <v>-0.1165757483892361</v>
       </c>
       <c r="U20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>-0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.04468158215747921</v>
+        <v>0.1544396386451896</v>
       </c>
       <c r="X20" t="n">
-        <v>0.04915980445873799</v>
+        <v>0.05834774303840588</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -11319,25 +11319,25 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.09397738437547734</v>
+        <v>-0.01060400893008473</v>
       </c>
       <c r="AD20" t="n">
         <v>-0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.04272001079871132</v>
+        <v>0.2508401875204844</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.04567183750646853</v>
+        <v>0.1716126959671651</v>
       </c>
       <c r="AH20" t="n">
         <v>-0</v>
@@ -11352,22 +11352,22 @@
         <v>-0</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.04028040565363836</v>
+        <v>-0.08938974722355786</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN20" t="n">
         <v>-0</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.03343058032541105</v>
+        <v>-0.07141031188667379</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.1013374147220494</v>
+        <v>0.1419350850785697</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -11379,19 +11379,19 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>-0.3496123901370689</v>
+        <v>-0.6149150868424663</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.1176416667378131</v>
+        <v>0.05124918492133224</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.4159167410334281</v>
+        <v>0.2723188853781366</v>
       </c>
       <c r="AZ20" t="n">
         <v>-0</v>
@@ -11400,13 +11400,13 @@
         <v>-0</v>
       </c>
       <c r="BB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
         <v>-0</v>
       </c>
       <c r="BD20" t="n">
-        <v>-0.1363276258712861</v>
+        <v>0.08170203648854645</v>
       </c>
       <c r="BE20" t="n">
         <v>-0</v>
@@ -11415,10 +11415,10 @@
         <v>-0</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.07804823697946346</v>
+        <v>0.2336195409683079</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.1334109812523011</v>
+        <v>0.1525195406289848</v>
       </c>
       <c r="BI20" t="n">
         <v>-0</v>
@@ -11430,10 +11430,10 @@
         <v>-0</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM20" t="n">
-        <v>-0.06437718804027238</v>
+        <v>-0.02808547196251074</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
@@ -11442,13 +11442,13 @@
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>-0.05677652824897449</v>
+        <v>-0.1385188322066593</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.0167280044953449</v>
+        <v>-0.02112653033162911</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS20" t="n">
         <v>-0</v>
@@ -11460,22 +11460,22 @@
         <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>-0.1814432584153705</v>
+        <v>-0.3609464324788373</v>
       </c>
       <c r="BW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX20" t="n">
         <v>-0</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.05096246965670754</v>
+        <v>0.08540976179636547</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.2442437851956338</v>
+        <v>0.2468978629782147</v>
       </c>
       <c r="CA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="n">
         <v>0</v>
@@ -11487,22 +11487,22 @@
         <v>0</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.09563317152722253</v>
+        <v>0.1353737942335806</v>
       </c>
       <c r="CF20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG20" t="n">
         <v>0</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.001868486598459206</v>
+        <v>-0.03001118606419656</v>
       </c>
       <c r="CI20" t="n">
-        <v>-0.1280446536226048</v>
+        <v>-0.15401869209775</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK20" t="n">
         <v>-0</v>
@@ -11514,7 +11514,7 @@
         <v>-0</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.0412637418483278</v>
+        <v>0.2269538224178695</v>
       </c>
       <c r="CO20" t="n">
         <v>-0</v>
@@ -11523,13 +11523,13 @@
         <v>0</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.09548358933826835</v>
+        <v>-0.2482769967602448</v>
       </c>
       <c r="CR20" t="n">
-        <v>0.03347332754688526</v>
+        <v>-0.2056955870139079</v>
       </c>
       <c r="CS20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT20" t="n">
         <v>0</v>
@@ -11538,25 +11538,25 @@
         <v>0</v>
       </c>
       <c r="CV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW20" t="n">
-        <v>0.06836744339993493</v>
+        <v>0.1190269201676349</v>
       </c>
       <c r="CX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY20" t="n">
         <v>-0</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.005964797800183227</v>
+        <v>-0.02170763906877115</v>
       </c>
       <c r="DA20" t="n">
-        <v>-0.1292388377225533</v>
+        <v>-0.153686291184802</v>
       </c>
       <c r="DB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC20" t="n">
         <v>0</v>
@@ -11568,52 +11568,52 @@
         <v>-0</v>
       </c>
       <c r="DF20" t="n">
-        <v>0.03522074379844873</v>
+        <v>0.02602821044456436</v>
       </c>
       <c r="DG20" t="n">
         <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.0451292987198296</v>
+        <v>0.143457207551632</v>
       </c>
       <c r="DJ20" t="n">
-        <v>-0.002096138166662609</v>
+        <v>0.01221123357026819</v>
       </c>
       <c r="DK20" t="n">
         <v>-0</v>
       </c>
       <c r="DL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO20" t="n">
-        <v>0.02082847349919064</v>
+        <v>0.05983620482545693</v>
       </c>
       <c r="DP20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ20" t="n">
         <v>-0</v>
       </c>
       <c r="DR20" t="n">
-        <v>0.01169424518701359</v>
+        <v>-0.05691653126968155</v>
       </c>
       <c r="DS20" t="n">
-        <v>-0.04839778300533853</v>
+        <v>-0.0194603711054358</v>
       </c>
       <c r="DT20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV20" t="n">
         <v>0</v>
@@ -11622,103 +11622,103 @@
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>-0.01373815011721641</v>
+        <v>-0.08857196490501922</v>
       </c>
       <c r="DY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA20" t="n">
-        <v>0.04125175225901213</v>
+        <v>-0.02305623465380945</v>
       </c>
       <c r="EB20" t="n">
-        <v>-0.03921136714938062</v>
+        <v>-0.09701524717326272</v>
       </c>
       <c r="EC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE20" t="n">
         <v>0</v>
       </c>
       <c r="EF20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG20" t="n">
-        <v>0.05876603620853781</v>
+        <v>0.01797715629432751</v>
       </c>
       <c r="EH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ20" t="n">
-        <v>-0.06697709981787055</v>
+        <v>0.06633794866875849</v>
       </c>
       <c r="EK20" t="n">
-        <v>-0.1187965508257458</v>
+        <v>-0.04674716205997467</v>
       </c>
       <c r="EL20" t="n">
         <v>0</v>
       </c>
       <c r="EM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP20" t="n">
-        <v>0.05477361947891703</v>
+        <v>0.03522483360979681</v>
       </c>
       <c r="EQ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER20" t="n">
         <v>0</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.03807295209295621</v>
+        <v>0.03417440531574344</v>
       </c>
       <c r="ET20" t="n">
-        <v>-0.008960976612050451</v>
+        <v>-0.09140359651574274</v>
       </c>
       <c r="EU20" t="n">
         <v>-0</v>
       </c>
       <c r="EV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY20" t="n">
-        <v>0.06711425615821572</v>
+        <v>0.1421204180030103</v>
       </c>
       <c r="EZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB20" t="n">
-        <v>-0.0186092983772505</v>
+        <v>-8.114730177647684e-05</v>
       </c>
       <c r="FC20" t="n">
-        <v>-0.1237551099324788</v>
+        <v>-0.1451321065658844</v>
       </c>
       <c r="FD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE20" t="n">
         <v>-0</v>
@@ -11730,34 +11730,34 @@
         <v>-0</v>
       </c>
       <c r="FH20" t="n">
-        <v>0.05165863531889633</v>
+        <v>0.153753685851329</v>
       </c>
       <c r="FI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ20" t="n">
         <v>0</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.02357539816790319</v>
+        <v>-0.0412854336283522</v>
       </c>
       <c r="FL20" t="n">
-        <v>0.09284515781444785</v>
+        <v>0.1845761019107228</v>
       </c>
       <c r="FM20" t="n">
         <v>-0</v>
       </c>
       <c r="FN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP20" t="n">
         <v>-0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.003168337348758927</v>
+        <v>0.02953155875099928</v>
       </c>
       <c r="FR20" t="n">
         <v>0</v>
@@ -11766,10 +11766,10 @@
         <v>0</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.001305324771699856</v>
+        <v>3.931547984264331e-05</v>
       </c>
       <c r="FU20" t="n">
-        <v>-0.05248366356703922</v>
+        <v>-0.1639671128683699</v>
       </c>
       <c r="FV20" t="n">
         <v>0</v>
@@ -11778,31 +11778,31 @@
         <v>-0</v>
       </c>
       <c r="FX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.02371463551229076</v>
+        <v>0.04706252062347626</v>
       </c>
       <c r="GA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB20" t="n">
         <v>0</v>
       </c>
       <c r="GC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.03277649065415175</v>
+        <v>-0.001856665556442917</v>
       </c>
       <c r="GE20" t="n">
         <v>0</v>
       </c>
       <c r="GF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG20" t="n">
         <v>-0</v>
@@ -11813,49 +11813,49 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>0.4207407582783952</v>
+        <v>0.2894280728202719</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1057680806656078</v>
+        <v>-0.08926589440868546</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.06614013104404462</v>
+        <v>0.01104583938908595</v>
       </c>
       <c r="F21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.344898224608627</v>
+        <v>0.3498072053445712</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1246645582748916</v>
+        <v>-0.1381725407518589</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.08548388747449838</v>
+        <v>-0.02471436007606851</v>
       </c>
       <c r="O21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -11864,22 +11864,22 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1058243800424973</v>
+        <v>0.05660298421579375</v>
       </c>
       <c r="U21" t="n">
         <v>-0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.01415784092786805</v>
+        <v>-0.002986185362387166</v>
       </c>
       <c r="W21" t="n">
-        <v>0.07668508086118024</v>
+        <v>-0.02329246113861204</v>
       </c>
       <c r="X21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>-0</v>
@@ -11891,127 +11891,127 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.09342615938797148</v>
+        <v>-0.03089176053648323</v>
       </c>
       <c r="AD21" t="n">
         <v>-0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.01372511832776135</v>
+        <v>-0.130756318587823</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.006778646018672934</v>
+        <v>-0.05857217581944753</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.00726728785169232</v>
+        <v>0.06290588004119031</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>-0.03849531132134775</v>
+        <v>-0.0318219062891698</v>
       </c>
       <c r="AO21" t="n">
-        <v>-0.06837206553982138</v>
+        <v>0.011605887206839</v>
       </c>
       <c r="AP21" t="n">
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS21" t="n">
         <v>-0</v>
       </c>
       <c r="AT21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.2825432897005961</v>
+        <v>0.2669556041286597</v>
       </c>
       <c r="AV21" t="n">
         <v>-0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.01117265865013376</v>
+        <v>-0.1172460173719837</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.1050154596940906</v>
+        <v>-0.1158316508064882</v>
       </c>
       <c r="AY21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
         <v>-0</v>
       </c>
       <c r="BC21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>0.05940438651593592</v>
+        <v>-0.02726102285854659</v>
       </c>
       <c r="BE21" t="n">
         <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>-0.06207979295017589</v>
+        <v>0.008302881253147223</v>
       </c>
       <c r="BG21" t="n">
-        <v>-0.1125931060130989</v>
+        <v>-0.01632758866613903</v>
       </c>
       <c r="BH21" t="n">
         <v>0</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL21" t="n">
         <v>-0</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.06001821980777427</v>
+        <v>0.02545269738953294</v>
       </c>
       <c r="BN21" t="n">
         <v>-0</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.01248016243682259</v>
+        <v>0.009381868430927967</v>
       </c>
       <c r="BP21" t="n">
-        <v>0.1742850571410473</v>
+        <v>0.04391918025266035</v>
       </c>
       <c r="BQ21" t="n">
         <v>-0</v>
@@ -12023,55 +12023,55 @@
         <v>-0</v>
       </c>
       <c r="BT21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.1413633229110826</v>
+        <v>0.2111108182919833</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>0.03786953959328373</v>
+        <v>-0.09371528096319073</v>
       </c>
       <c r="BY21" t="n">
-        <v>0.08541862479101886</v>
+        <v>0.006265966044022678</v>
       </c>
       <c r="BZ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE21" t="n">
-        <v>-0.08509261325521747</v>
+        <v>-0.07618543844134781</v>
       </c>
       <c r="CF21" t="n">
         <v>-0</v>
       </c>
       <c r="CG21" t="n">
-        <v>0.01069910619404409</v>
+        <v>0.07141080873932081</v>
       </c>
       <c r="CH21" t="n">
-        <v>-0.004751237532125739</v>
+        <v>0.01124741693550737</v>
       </c>
       <c r="CI21" t="n">
         <v>0</v>
       </c>
       <c r="CJ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK21" t="n">
         <v>0</v>
@@ -12083,52 +12083,52 @@
         <v>0</v>
       </c>
       <c r="CN21" t="n">
-        <v>-0.05696423441630818</v>
+        <v>-0.1116100693847247</v>
       </c>
       <c r="CO21" t="n">
         <v>-0</v>
       </c>
       <c r="CP21" t="n">
-        <v>-0.07944349286456209</v>
+        <v>0.1288055883807946</v>
       </c>
       <c r="CQ21" t="n">
-        <v>-0.1119013589346013</v>
+        <v>0.03285217278870046</v>
       </c>
       <c r="CR21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS21" t="n">
         <v>-0</v>
       </c>
       <c r="CT21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW21" t="n">
-        <v>-0.07391771015257588</v>
+        <v>-0.06744018262251143</v>
       </c>
       <c r="CX21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY21" t="n">
-        <v>0.02626905894571118</v>
+        <v>0.07801614593175724</v>
       </c>
       <c r="CZ21" t="n">
-        <v>-0.006689934287718516</v>
+        <v>0.002148479777851462</v>
       </c>
       <c r="DA21" t="n">
         <v>-0</v>
       </c>
       <c r="DB21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD21" t="n">
         <v>0</v>
@@ -12137,211 +12137,211 @@
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>-0.07141853557554</v>
+        <v>-0.06640517256681823</v>
       </c>
       <c r="DG21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH21" t="n">
-        <v>0.01134601792306502</v>
+        <v>0.0443842578812125</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.01985261913270829</v>
+        <v>-0.08483807546908673</v>
       </c>
       <c r="DJ21" t="n">
         <v>-0</v>
       </c>
       <c r="DK21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL21" t="n">
         <v>0</v>
       </c>
       <c r="DM21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN21" t="n">
         <v>-0</v>
       </c>
       <c r="DO21" t="n">
-        <v>-0.03286758628912744</v>
+        <v>-0.04474990588574503</v>
       </c>
       <c r="DP21" t="n">
         <v>0</v>
       </c>
       <c r="DQ21" t="n">
-        <v>-0.1210160496938121</v>
+        <v>-0.01701446958669111</v>
       </c>
       <c r="DR21" t="n">
-        <v>-0.02826847065997855</v>
+        <v>0.01267281363831739</v>
       </c>
       <c r="DS21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX21" t="n">
-        <v>-0.07961023745249052</v>
+        <v>0.02476425292604009</v>
       </c>
       <c r="DY21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ21" t="n">
-        <v>0.004064416429594918</v>
+        <v>-0.02473543802547052</v>
       </c>
       <c r="EA21" t="n">
-        <v>0.03293975564082362</v>
+        <v>-0.02094825654053888</v>
       </c>
       <c r="EB21" t="n">
         <v>0</v>
       </c>
       <c r="EC21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG21" t="n">
-        <v>-0.08502341726040563</v>
+        <v>-0.03586530444938027</v>
       </c>
       <c r="EH21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI21" t="n">
-        <v>-0.06066832725731706</v>
+        <v>-0.1374647279043767</v>
       </c>
       <c r="EJ21" t="n">
-        <v>0.07269801013394418</v>
+        <v>0.003725484974269903</v>
       </c>
       <c r="EK21" t="n">
         <v>0</v>
       </c>
       <c r="EL21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN21" t="n">
         <v>-0</v>
       </c>
       <c r="EO21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP21" t="n">
-        <v>-0.05963753531932518</v>
+        <v>-0.05037276725371485</v>
       </c>
       <c r="EQ21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER21" t="n">
-        <v>0.03393832511731459</v>
+        <v>0.02599430558812485</v>
       </c>
       <c r="ES21" t="n">
-        <v>0.02106246991945144</v>
+        <v>-0.0305221342546939</v>
       </c>
       <c r="ET21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY21" t="n">
-        <v>-0.0757303959479048</v>
+        <v>-0.08287193041745955</v>
       </c>
       <c r="EZ21" t="n">
         <v>-0</v>
       </c>
       <c r="FA21" t="n">
-        <v>0.008392059306536886</v>
+        <v>0.08069764603186527</v>
       </c>
       <c r="FB21" t="n">
-        <v>0.01036374921147554</v>
+        <v>-0.004208828787158637</v>
       </c>
       <c r="FC21" t="n">
         <v>0</v>
       </c>
       <c r="FD21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF21" t="n">
         <v>-0</v>
       </c>
       <c r="FG21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH21" t="n">
-        <v>-0.04451910997438841</v>
+        <v>0.08447431107588152</v>
       </c>
       <c r="FI21" t="n">
         <v>-0</v>
       </c>
       <c r="FJ21" t="n">
-        <v>0.0492682343527534</v>
+        <v>0.1008781539525718</v>
       </c>
       <c r="FK21" t="n">
-        <v>0.05190337132649394</v>
+        <v>-0.01231577188965889</v>
       </c>
       <c r="FL21" t="n">
         <v>-0</v>
       </c>
       <c r="FM21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO21" t="n">
         <v>0</v>
       </c>
       <c r="FP21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ21" t="n">
-        <v>0.02195518555359808</v>
+        <v>-0.06533093632236288</v>
       </c>
       <c r="FR21" t="n">
         <v>-0</v>
       </c>
       <c r="FS21" t="n">
-        <v>0.0398098162714226</v>
+        <v>0.04345220117756576</v>
       </c>
       <c r="FT21" t="n">
-        <v>-0.008674086492441094</v>
+        <v>0.07668656573105127</v>
       </c>
       <c r="FU21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW21" t="n">
         <v>-0</v>
@@ -12350,31 +12350,31 @@
         <v>0</v>
       </c>
       <c r="FY21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ21" t="n">
-        <v>0.01907278246302546</v>
+        <v>-0.07285871371061528</v>
       </c>
       <c r="GA21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB21" t="n">
-        <v>-0.07891588057507001</v>
+        <v>0.02800803408491075</v>
       </c>
       <c r="GC21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
